--- a/outputs/tables/tab2_countries.xlsx
+++ b/outputs/tables/tab2_countries.xlsx
@@ -6,18 +6,18 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabla" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Table" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="209">
-  <si>
-    <t xml:space="preserve">Tabla 2. Subsidio explícito a combustibles fósiles por país y año (% del PIB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">País</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="210">
+  <si>
+    <t xml:space="preserve">Table 2. Explicit fossil fuel subsidy by country and year (% of GDP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Country</t>
   </si>
   <si>
     <t xml:space="preserve">2015</t>
@@ -47,10 +47,10 @@
     <t xml:space="preserve">2023</t>
   </si>
   <si>
-    <t xml:space="preserve">Cambio (pp)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panel A. Exportadores netos de hidrocarburos</t>
+    <t xml:space="preserve">Change (pp)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panel A. Net oil exporters</t>
   </si>
   <si>
     <t xml:space="preserve"/>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">1.02</t>
   </si>
   <si>
-    <t xml:space="preserve">  México</t>
+    <t xml:space="preserve">  Mexico</t>
   </si>
   <si>
     <t xml:space="preserve">0.64</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">0.85</t>
   </si>
   <si>
-    <t xml:space="preserve">  Trinidad y Tobago</t>
+    <t xml:space="preserve">  Trinidad and Tobago</t>
   </si>
   <si>
     <t xml:space="preserve">3.04</t>
@@ -275,16 +275,16 @@
     <t xml:space="preserve">0.41</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  N (países) = 7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panel B. Importadores netos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Surinam</t>
+    <t xml:space="preserve">−0.27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  N (countries) = 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panel B. Net oil importers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Suriname</t>
   </si>
   <si>
     <t xml:space="preserve">3.32</t>
@@ -341,7 +341,7 @@
     <t xml:space="preserve">2.33</t>
   </si>
   <si>
-    <t xml:space="preserve">  Haití</t>
+    <t xml:space="preserve">  Haiti</t>
   </si>
   <si>
     <t xml:space="preserve">0.10</t>
@@ -371,7 +371,7 @@
     <t xml:space="preserve">1.66</t>
   </si>
   <si>
-    <t xml:space="preserve">  República Dominicana</t>
+    <t xml:space="preserve">  Dominican Republic</t>
   </si>
   <si>
     <t xml:space="preserve">0.53</t>
@@ -395,7 +395,7 @@
     <t xml:space="preserve">1.25</t>
   </si>
   <si>
-    <t xml:space="preserve">  Belice</t>
+    <t xml:space="preserve">  Belize</t>
   </si>
   <si>
     <t xml:space="preserve">0.05</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">0.27</t>
   </si>
   <si>
-    <t xml:space="preserve">  Antigua y Barbuda</t>
+    <t xml:space="preserve">  Antigua and Barbuda</t>
   </si>
   <si>
     <t xml:space="preserve">0.37</t>
@@ -536,7 +536,7 @@
     <t xml:space="preserve">0.25</t>
   </si>
   <si>
-    <t xml:space="preserve">  Perú</t>
+    <t xml:space="preserve">  Peru</t>
   </si>
   <si>
     <t xml:space="preserve">0.02</t>
@@ -560,7 +560,7 @@
     <t xml:space="preserve">  Costa Rica</t>
   </si>
   <si>
-    <t xml:space="preserve">  Panamá</t>
+    <t xml:space="preserve">  Panama</t>
   </si>
   <si>
     <t xml:space="preserve">0.06</t>
@@ -575,6 +575,9 @@
     <t xml:space="preserve">  Puerto Rico</t>
   </si>
   <si>
+    <t xml:space="preserve">n.a.</t>
+  </si>
+  <si>
     <t xml:space="preserve">  Bahamas</t>
   </si>
   <si>
@@ -593,52 +596,52 @@
     <t xml:space="preserve">0.29</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Brasil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  San Vicente y las Granadinas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  San Cristóbal y Nieves</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.07</t>
+    <t xml:space="preserve">−0.01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Brazil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">−0.02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  St. Vincent and the Grenadines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">−0.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  St. Kitts and Nevis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">−0.07</t>
   </si>
   <si>
     <t xml:space="preserve">  Chile</t>
   </si>
   <si>
-    <t xml:space="preserve">  Santa Lucía</t>
+    <t xml:space="preserve">  St. Lucia</t>
   </si>
   <si>
     <t xml:space="preserve">0.22</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Granada</t>
+    <t xml:space="preserve">−0.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Grenada</t>
   </si>
   <si>
     <t xml:space="preserve">1.24</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  N (países) = 27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notas. Subsidio explícito a los combustibles fósiles como porcentaje del PIB, por país y año, alrededor del choque petrolero de 2022. La última columna es el cambio del choque en puntos porcentuales: el valor de 2022 menos el promedio del período pre-choque (2015-2021). Los países se ordenan por la magnitud del cambio dentro de cada panel. Un valor de 0.00 indica que el país no aplica subsidio explícito (precio al consumidor por encima del costo de suministro). La clasificación es por exposición fiscal neta al precio del petróleo, no por producción: en los exportadores netos el alza del Brent infla la renta petrolera que financia el subsidio, mientras que en los importadores netos encarece el costo de suministro y agrava el gasto. Argentina (importador neto de energía en el período) y Brasil (importa los derivados refinados que se subsidian) se clasifican como importadores. Panel A, exportadores netos de hidrocarburos (N = 7): Bolivia, Colombia, Ecuador, Guyana, México, Trinidad y Tobago, Venezuela. Panel B, importadores netos (N = 27): Antigua y Barbuda, Argentina, Aruba, Bahamas, Barbados, Belice, Brasil, Chile, Costa Rica, Dominica, El Salvador, Granada, Guatemala, Haití, Honduras, Jamaica, Nicaragua, Panamá, Paraguay, Perú, Puerto Rico, República Dominicana, San Cristóbal y Nieves, San Vicente y las Granadinas, Santa Lucía, Surinam, Uruguay. Fuente: IMF Fossil Fuel Subsidies Database.</t>
+    <t xml:space="preserve">−0.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  N (countries) = 27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes. Explicit fossil fuel subsidy as a percentage of GDP, by country and year. Change (pp): 2022 value minus the 2015–2021 average, in percentage points; countries are sorted by this change within each panel. A value of 0.00 indicates a subsidy below 0.005% of GDP; n.a.: not available (Puerto Rico 2015–2017). Countries are classified by net oil trade position, not by production (seven net oil exporters and 27 net oil importers). Source: IMF Fossil Fuel Subsidies Database.</t>
   </si>
 </sst>
 </file>
@@ -2086,13 +2089,13 @@
         <v>186</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>13</v>
+        <v>187</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>13</v>
+        <v>187</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>13</v>
+        <v>187</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>144</v>
@@ -2118,7 +2121,7 @@
     </row>
     <row r="32">
       <c r="B32" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>143</v>
@@ -2153,7 +2156,7 @@
     </row>
     <row r="33">
       <c r="B33" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>164</v>
@@ -2165,30 +2168,30 @@
         <v>151</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G33" s="4" t="s">
         <v>172</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I33" s="4" t="s">
         <v>136</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>129</v>
@@ -2218,12 +2221,12 @@
         <v>129</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>147</v>
@@ -2253,12 +2256,12 @@
         <v>144</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>167</v>
@@ -2288,12 +2291,12 @@
         <v>144</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>149</v>
@@ -2323,21 +2326,21 @@
         <v>145</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>151</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>61</v>
@@ -2352,21 +2355,21 @@
         <v>168</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K38" s="4" t="s">
         <v>149</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>140</v>
@@ -2381,7 +2384,7 @@
         <v>172</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I39" s="4" t="s">
         <v>164</v>
@@ -2393,12 +2396,12 @@
         <v>167</v>
       </c>
       <c r="L39" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>13</v>
@@ -2431,9 +2434,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" ht="125" customHeight="1">
+    <row r="41" ht="50" customHeight="1">
       <c r="B41" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tables/tab2_countries.xlsx
+++ b/outputs/tables/tab2_countries.xlsx
@@ -89,6 +89,126 @@
     <t xml:space="preserve">6.12</t>
   </si>
   <si>
+    <t xml:space="preserve">  Colombia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Ecuador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Trinidad and Tobago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Brazil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">−0.02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  N (countries) = 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panel B. Net oil importers</t>
+  </si>
+  <si>
     <t xml:space="preserve">  Bolivia</t>
   </si>
   <si>
@@ -119,67 +239,118 @@
     <t xml:space="preserve">5.38</t>
   </si>
   <si>
-    <t xml:space="preserve">  Colombia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Ecuador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02</t>
+    <t xml:space="preserve">  Suriname</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Argentina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Haiti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Dominican Republic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25</t>
   </si>
   <si>
     <t xml:space="preserve">  Mexico</t>
@@ -206,43 +377,241 @@
     <t xml:space="preserve">1.64</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.85</t>
   </si>
   <si>
-    <t xml:space="preserve">  Trinidad and Tobago</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.74</t>
+    <t xml:space="preserve">  Belize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  El Salvador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Nicaragua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Jamaica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Honduras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Guatemala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Antigua and Barbuda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Peru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Dominica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Uruguay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Costa Rica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Panama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Paraguay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Aruba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Puerto Rico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n.a.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Bahamas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Barbados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">−0.01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  St. Vincent and the Grenadines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">−0.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  St. Kitts and Nevis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">−0.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Chile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  St. Lucia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">−0.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Grenada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">−0.26</t>
   </si>
   <si>
     <t xml:space="preserve">  Guyana</t>
@@ -260,388 +629,19 @@
     <t xml:space="preserve">1.28</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.22</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.77</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41</t>
-  </si>
-  <si>
     <t xml:space="preserve">−0.27</t>
   </si>
   <si>
-    <t xml:space="preserve">  N (countries) = 7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panel B. Net oil importers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Suriname</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Argentina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Haiti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Dominican Republic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Belize</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.82</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  El Salvador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Nicaragua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Jamaica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.76</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Honduras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Guatemala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Antigua and Barbuda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Peru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Dominica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Uruguay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Costa Rica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Panama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Paraguay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Aruba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Puerto Rico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n.a.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Bahamas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Barbados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">−0.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Brazil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">−0.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  St. Vincent and the Grenadines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">−0.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  St. Kitts and Nevis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">−0.07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Chile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  St. Lucia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">−0.09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Grenada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">−0.26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  N (countries) = 27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notes. Explicit fossil fuel subsidy as a percentage of GDP, by country and year. Change (pp): 2022 value minus the 2015–2021 average, in percentage points; countries are sorted by this change within each panel. A value of 0.00 indicates a subsidy below 0.005% of GDP; n.a.: not available (Puerto Rico 2015–2017). Countries are classified by net oil trade position, not by production (seven net oil exporters and 27 net oil importers). Source: IMF Fossil Fuel Subsidies Database.</t>
+    <t xml:space="preserve">  N (countries) = 29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes. Explicit fossil fuel subsidy as a percentage of GDP, by country and year. Change (pp): 2022 value minus the 2015–2021 average, in percentage points; countries are sorted by this change within each panel. A value of 0.00 indicates a subsidy below 0.005% of GDP; n.a.: not available (Puerto Rico 2015–2017). Countries are classified by net oil trade position (average 2015–2019 net exports of crude oil and refined products, UN Comtrade), not by production (five net oil exporters and 29 net oil importers). Puerto Rico, absent from UN Comtrade, is classified as a net oil importer from U.S. Energy Information Administration data. Source: IMF Fossil Fuel Subsidies Database; UN Comtrade.</t>
   </si>
 </sst>
 </file>
@@ -1188,10 +1188,10 @@
         <v>28</v>
       </c>
       <c r="F5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>30</v>
@@ -1223,74 +1223,74 @@
         <v>38</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>55</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>59</v>
@@ -1302,1098 +1302,1098 @@
         <v>61</v>
       </c>
       <c r="I8" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="L8" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="J8" s="4" t="s">
+    </row>
+    <row r="9">
+      <c r="B9" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="C9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="L8" s="4" t="s">
+      <c r="C10" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="3" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="F11" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="G11" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="I11" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="J11" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="K11" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="L11" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="K9" s="4" t="s">
+    </row>
+    <row r="12">
+      <c r="B12" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="L9" s="4" t="s">
+      <c r="C12" s="4" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="3" t="s">
+      <c r="D12" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="E12" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="F12" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="G12" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="H12" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="I12" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="J12" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="K12" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="L12" s="4" t="s">
         <v>85</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="K11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="L11" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J12" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K12" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="H13" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="I13" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J13" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="K13" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>99</v>
-      </c>
       <c r="L13" s="4" t="s">
-        <v>100</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="I14" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="J14" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E14" s="4" t="s">
+      <c r="K14" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>108</v>
-      </c>
       <c r="L14" s="4" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="J15" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="K15" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="L15" s="4" t="s">
         <v>112</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="L15" s="4" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="I16" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="J16" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F16" s="4" t="s">
+      <c r="K16" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L16" s="4" t="s">
         <v>121</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="L16" s="4" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="L17" s="4" t="s">
         <v>127</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="L17" s="4" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="K18" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="L18" s="4" t="s">
         <v>135</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="L18" s="4" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="J19" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="K19" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L19" s="4" t="s">
         <v>143</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="L19" s="4" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="K20" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>159</v>
-      </c>
       <c r="L20" s="4" t="s">
-        <v>64</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="3" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="3" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>146</v>
+        <v>61</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>145</v>
+        <v>60</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K22" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="L22" s="4" t="s">
         <v>163</v>
-      </c>
-      <c r="L22" s="4" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>60</v>
+        <v>117</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="3" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>145</v>
+        <v>60</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="3" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>86</v>
+        <v>171</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>145</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="3" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>128</v>
+        <v>59</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>129</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>146</v>
+        <v>61</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>146</v>
+        <v>61</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>146</v>
+        <v>61</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>146</v>
+        <v>61</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="L27" s="4" t="s">
-        <v>129</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="3" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>145</v>
+        <v>60</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>128</v>
+        <v>59</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>128</v>
+        <v>59</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>146</v>
+        <v>61</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="3" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>86</v>
+        <v>171</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="3" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="3" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="3" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="3" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="3" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>128</v>
+        <v>28</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>129</v>
+        <v>61</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>128</v>
+        <v>61</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>145</v>
+        <v>58</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="3" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>146</v>
+        <v>28</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>146</v>
+        <v>60</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>129</v>
+        <v>177</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="3" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>167</v>
+        <v>141</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>38</v>
+        <v>124</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>145</v>
+        <v>27</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>144</v>
+        <v>26</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>144</v>
+        <v>61</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>144</v>
+        <v>60</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>110</v>
+        <v>186</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>130</v>
+        <v>187</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>37</v>
+        <v>118</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>169</v>
+        <v>106</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>36</v>
+        <v>161</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>151</v>
+        <v>198</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>192</v>
+        <v>134</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>193</v>
+        <v>91</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>61</v>
+        <v>130</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>64</v>
+        <v>186</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>203</v>
+        <v>142</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="H39" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="I39" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J39" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="D39" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="H39" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="I39" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="J39" s="4" t="s">
-        <v>150</v>
-      </c>
       <c r="K39" s="4" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="L39" s="4" t="s">
         <v>207</v>
@@ -2434,7 +2434,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" ht="50" customHeight="1">
+    <row r="41" ht="62.5" customHeight="1">
       <c r="B41" s="9" t="s">
         <v>209</v>
       </c>
